--- a/data/data_raw/eurostat/AT_cars_road_eqr_carpda.xlsx
+++ b/data/data_raw/eurostat/AT_cars_road_eqr_carpda.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,11 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -561,6 +566,9 @@
       </c>
       <c r="P2" t="n">
         <v>239150</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>253789</v>
       </c>
     </row>
     <row r="3">
@@ -620,6 +628,9 @@
       <c r="P3" t="n">
         <v>130321</v>
       </c>
+      <c r="Q3" t="n">
+        <v>150676</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -676,6 +687,9 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -734,6 +748,9 @@
       <c r="P5" t="n">
         <v>61187</v>
       </c>
+      <c r="Q5" t="n">
+        <v>58478</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -792,6 +809,9 @@
       <c r="P6" t="n">
         <v>6</v>
       </c>
+      <c r="Q6" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -850,6 +870,9 @@
       <c r="P7" t="n">
         <v>47621</v>
       </c>
+      <c r="Q7" t="n">
+        <v>44622</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -908,6 +931,9 @@
       <c r="P8" t="n">
         <v>47642</v>
       </c>
+      <c r="Q8" t="n">
+        <v>44635</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -966,6 +992,9 @@
       <c r="P9" t="n">
         <v>77354</v>
       </c>
+      <c r="Q9" t="n">
+        <v>84004</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1024,6 +1053,9 @@
       <c r="P10" t="n">
         <v>36705</v>
       </c>
+      <c r="Q10" t="n">
+        <v>51611</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1082,6 +1114,9 @@
       <c r="P11" t="n">
         <v>16262</v>
       </c>
+      <c r="Q11" t="n">
+        <v>15061</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1140,6 +1175,9 @@
       <c r="P12" t="n">
         <v>46568</v>
       </c>
+      <c r="Q12" t="n">
+        <v>44132</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1198,6 +1236,9 @@
       <c r="P13" t="n">
         <v>13925</v>
       </c>
+      <c r="Q13" t="n">
+        <v>12479</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1256,6 +1297,9 @@
       <c r="P14" t="n">
         <v>694</v>
       </c>
+      <c r="Q14" t="n">
+        <v>1867</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1313,6 +1357,9 @@
       </c>
       <c r="P15" t="n">
         <v>10</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1360,6 +1407,9 @@
       <c r="P16" t="n">
         <v>0</v>
       </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1406,6 +1456,9 @@
       <c r="P17" t="n">
         <v>0</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1464,6 +1517,9 @@
       <c r="P18" t="n">
         <v>5</v>
       </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1520,6 +1576,9 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0</v>
       </c>
     </row>
